--- a/data_extactor/batch_10_fa/trimmed/batch_0087_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0087_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | دید نزدیک | چابکی دستی | حساسیت به مسئله | تجسم فضایی | مرتب‌سازی اطلاعات</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌ابزار کنترل عددی رایانه‌ای CNC | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | حساسیت به مسئله | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو</t>
+          <t>تجسم | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | ماشین‌کاران و تراشکاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان صنعتی فلز و پلاستیک</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | چابکی انگشتان | دقت کنترل | چابکی دستی | استدلال قیاسی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | مهارت انگشتان | دقت کنترل | مهارت دستی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مونتاژکاران موتورها و ماشین‌آلات صنعتی | کارگران سنگ‌زنی و پرداخت‌کاری دستی | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران و تراشکاران صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | سازندگان و مونتاژکاران سازه‌های فلزی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | طراحی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | تجسم فضایی | ثبات دست و بازو | چابکی دستی | هماهنگی اندام‌ها | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | دقت کنترل | تجسم | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | مونتاژکاران موتورها و ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌کاران و تراشکاران صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAP | Microsoft Excel | Microsoft Word | Microsoft Outlook | Microsoft Office</t>
+          <t>SAP | نرم‌افزار Microsoft Office | Microsoft Word | Microsoft Outlook | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | هماهنگی اندام‌ها | زمان واکنش | دید نزدیک | چابکی دستی | حساسیت به مسئله | دقت کنترل</t>
+          <t>ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | دقت کنترل</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات شیمیایی | تنظیم‌کاران و اپراتورهای دستگاه‌های آهنگری فلز و پلاستیک | اپراتورهای کوره‌ها، خشک‌کن‌ها و دیگ‌های ذوب صنعتی | اپراتورهای کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | تجسم فضایی | حساسیت به مسئله | چابکی دستی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | تجسم | حساسیت به مسئله | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>دیگ‌سازان و مخزن‌سازان صنعتی | ماشین‌کاران و تراشکاران صنعتی | نقشه‌کشان مکانیک | مدل‌سازان صنعتی فلز و پلاستیک | الگو سازان قطعات فلزی و پلاستیکی | ورق‌کاران و کانال‌سازان فلزی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | مدل‌سازان فلز و پلاستیک | الگوسازان فلز و پلاستیک | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | هماهنگی اندام‌ها</t>
+          <t>بینایی نزدیک | دقت کنترل | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات شیمیایی | تنظیم‌کاران و اپراتورهای دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و اسپری | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین قطعات | تنظیم‌کاران و اپراتورهای دستگاه‌های جداسازی، فیلتراسیون و تقطیر صنعتی</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت کنترل | دید نزدیک | تجسم فضایی | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کاران و اپراتورهای دستگاه‌های مته‌کاری و سوراخ‌کاری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت‌کاری دستی | تنظیم‌کاران و اپراتورهای دستگاه‌های سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های تراشکاری فلز و پلاستیک | قالب‌سازان و ابزارسازان صنعتی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستای بدنی | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ماشین‌کاران و تراشکاران صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورهای ماشین‌ابزار کنترل عددی رایانه‌ای CNC | سازندگان و مونتاژکاران سازه‌های فلزی</t>
+          <t>تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | جوشکاران، برشکاران و لحیم‌کاران صنعتی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | سازندگان و مونتاژکاران سازه‌های فلزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ریاضیات | تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | تجسم فضایی | تشخیص تفاوت رنگ‌ها | مرتب‌سازی اطلاعات | درک کتبی | دقت کنترل</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | تجسم | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | درک کتبی | دقت کنترل</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>طراحان نشر رومیزی و صفحه‌آرایان | قلم‌زنان و حکاکان | اپراتورهای ماشین‌آلات اداری (به‌جز رایانه) | تنظیم‌کاران و اپراتورهای ماشین‌آلات تولید محصولات کاغذی | پرسنل ظهور عکس و اپراتورهای تجهیزات عکاسی | صحافان و کارگران پرداخت و تکمیل چاپ | اپراتورهای ماشین‌آلات چاپ</t>
+          <t>متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | حکاکان و اسیدکاران | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | کارگران صحافی و تکمیل چاپ | اپراتورهای ماشین‌های چاپ</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
